--- a/artfynd/A 20012-2024 artfynd.xlsx
+++ b/artfynd/A 20012-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118497445</v>
+        <v>118497715</v>
       </c>
       <c r="B2" t="n">
-        <v>57306</v>
+        <v>78484</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>676119</v>
+        <v>676188</v>
       </c>
       <c r="R2" t="n">
-        <v>7096878</v>
+        <v>7096815</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,12 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:17</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Gammalt hack</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -904,7 +899,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118497715</v>
+        <v>118497504</v>
       </c>
       <c r="B4" t="n">
         <v>78484</v>
@@ -944,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>676188</v>
+        <v>676121</v>
       </c>
       <c r="R4" t="n">
-        <v>7096815</v>
+        <v>7096880</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -979,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,7 +1011,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118497504</v>
+        <v>118712960</v>
       </c>
       <c r="B5" t="n">
         <v>78484</v>
@@ -1052,17 +1047,17 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Mittiliden (Mittiliden), Ång</t>
+          <t>A 20012-2024, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>676121</v>
+        <v>676387</v>
       </c>
       <c r="R5" t="n">
-        <v>7096880</v>
+        <v>7096519</v>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1089,19 +1084,9 @@
           <t>2024-07-17</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>11:24</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-07-17</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>11:24</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1116,12 +1101,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Richard Johansson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Ulrika Karlsson</t>
+          <t>Richard Johansson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1230,7 +1215,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118712960</v>
+        <v>118712963</v>
       </c>
       <c r="B7" t="n">
         <v>78484</v>
@@ -1270,10 +1255,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>676387</v>
+        <v>676196</v>
       </c>
       <c r="R7" t="n">
-        <v>7096519</v>
+        <v>7096796</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1434,10 +1419,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118712963</v>
+        <v>118497445</v>
       </c>
       <c r="B9" t="n">
-        <v>78484</v>
+        <v>57306</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1450,37 +1435,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>A 20012-2024, Ång</t>
+          <t>Mittiliden (Mittiliden), Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>676196</v>
+        <v>676119</v>
       </c>
       <c r="R9" t="n">
-        <v>7096796</v>
+        <v>7096878</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1507,9 +1492,24 @@
           <t>2024-07-17</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-07-17</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Gammalt hack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1524,12 +1524,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Richard Johansson</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Richard Johansson</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>

--- a/artfynd/A 20012-2024 artfynd.xlsx
+++ b/artfynd/A 20012-2024 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118498903</v>
+        <v>118497504</v>
       </c>
       <c r="B3" t="n">
-        <v>96801</v>
+        <v>78484</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,25 +799,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>676528</v>
+        <v>676121</v>
       </c>
       <c r="R3" t="n">
-        <v>7096810</v>
+        <v>7096880</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118497504</v>
+        <v>118498903</v>
       </c>
       <c r="B4" t="n">
-        <v>78484</v>
+        <v>96801</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,25 +911,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>676121</v>
+        <v>676528</v>
       </c>
       <c r="R4" t="n">
-        <v>7096880</v>
+        <v>7096810</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,7 +1011,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118712960</v>
+        <v>118712961</v>
       </c>
       <c r="B5" t="n">
         <v>78484</v>
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>676387</v>
+        <v>676420</v>
       </c>
       <c r="R5" t="n">
-        <v>7096519</v>
+        <v>7096841</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1113,7 +1113,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118712961</v>
+        <v>118712963</v>
       </c>
       <c r="B6" t="n">
         <v>78484</v>
@@ -1153,10 +1153,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>676420</v>
+        <v>676196</v>
       </c>
       <c r="R6" t="n">
-        <v>7096841</v>
+        <v>7096796</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1215,7 +1215,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118712963</v>
+        <v>118712960</v>
       </c>
       <c r="B7" t="n">
         <v>78484</v>
@@ -1255,10 +1255,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>676196</v>
+        <v>676387</v>
       </c>
       <c r="R7" t="n">
-        <v>7096796</v>
+        <v>7096519</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 20012-2024 artfynd.xlsx
+++ b/artfynd/A 20012-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118497715</v>
+        <v>118498903</v>
       </c>
       <c r="B2" t="n">
-        <v>78484</v>
+        <v>96808</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>676188</v>
+        <v>676528</v>
       </c>
       <c r="R2" t="n">
-        <v>7096815</v>
+        <v>7096810</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,7 +790,7 @@
         <v>118497504</v>
       </c>
       <c r="B3" t="n">
-        <v>78484</v>
+        <v>78491</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118498903</v>
+        <v>118497715</v>
       </c>
       <c r="B4" t="n">
-        <v>96801</v>
+        <v>78491</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,25 +911,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>676528</v>
+        <v>676188</v>
       </c>
       <c r="R4" t="n">
-        <v>7096810</v>
+        <v>7096815</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118712961</v>
+        <v>118712963</v>
       </c>
       <c r="B5" t="n">
-        <v>78484</v>
+        <v>78491</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>676420</v>
+        <v>676196</v>
       </c>
       <c r="R5" t="n">
-        <v>7096841</v>
+        <v>7096796</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1113,10 +1113,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118712963</v>
+        <v>118712962</v>
       </c>
       <c r="B6" t="n">
-        <v>78484</v>
+        <v>78491</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1153,10 +1153,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>676196</v>
+        <v>676262</v>
       </c>
       <c r="R6" t="n">
-        <v>7096796</v>
+        <v>7096822</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1218,7 +1218,7 @@
         <v>118712960</v>
       </c>
       <c r="B7" t="n">
-        <v>78484</v>
+        <v>78491</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1317,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118712962</v>
+        <v>118712961</v>
       </c>
       <c r="B8" t="n">
-        <v>78484</v>
+        <v>78491</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>676262</v>
+        <v>676420</v>
       </c>
       <c r="R8" t="n">
-        <v>7096822</v>
+        <v>7096841</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>

--- a/artfynd/A 20012-2024 artfynd.xlsx
+++ b/artfynd/A 20012-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118498903</v>
+        <v>118497715</v>
       </c>
       <c r="B2" t="n">
-        <v>96808</v>
+        <v>78491</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>676528</v>
+        <v>676188</v>
       </c>
       <c r="R2" t="n">
-        <v>7096810</v>
+        <v>7096815</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118497504</v>
+        <v>118498903</v>
       </c>
       <c r="B3" t="n">
-        <v>78491</v>
+        <v>96808</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,25 +799,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>676121</v>
+        <v>676528</v>
       </c>
       <c r="R3" t="n">
-        <v>7096880</v>
+        <v>7096810</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,7 +899,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118497715</v>
+        <v>118497504</v>
       </c>
       <c r="B4" t="n">
         <v>78491</v>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>676188</v>
+        <v>676121</v>
       </c>
       <c r="R4" t="n">
-        <v>7096815</v>
+        <v>7096880</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,7 +1011,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118712963</v>
+        <v>118712960</v>
       </c>
       <c r="B5" t="n">
         <v>78491</v>
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>676196</v>
+        <v>676387</v>
       </c>
       <c r="R5" t="n">
-        <v>7096796</v>
+        <v>7096519</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1113,7 +1113,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118712962</v>
+        <v>118712961</v>
       </c>
       <c r="B6" t="n">
         <v>78491</v>
@@ -1153,10 +1153,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>676262</v>
+        <v>676420</v>
       </c>
       <c r="R6" t="n">
-        <v>7096822</v>
+        <v>7096841</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1215,7 +1215,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118712960</v>
+        <v>118712963</v>
       </c>
       <c r="B7" t="n">
         <v>78491</v>
@@ -1255,10 +1255,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>676387</v>
+        <v>676196</v>
       </c>
       <c r="R7" t="n">
-        <v>7096519</v>
+        <v>7096796</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1317,7 +1317,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118712961</v>
+        <v>118712962</v>
       </c>
       <c r="B8" t="n">
         <v>78491</v>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>676420</v>
+        <v>676262</v>
       </c>
       <c r="R8" t="n">
-        <v>7096841</v>
+        <v>7096822</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
